--- a/output/广东/广东_battle3.xlsx
+++ b/output/广东/广东_battle3.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L126"/>
+  <dimension ref="A1:L125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="41" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -1000,25 +1000,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>朱森林</t>
+          <t>卢瑞华</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京市公安局外三分局派出所</t>
+          <t>广东省佛山市分析仪器厂</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>副所长、代所长、所长</t>
+          <t>厂长</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>副科级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1033,16 +1033,16 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>北京市公安分局派出所所长通常为副科级</t>
+          <t>仅知厂长和厂名，单位隶属规模不明，难定级</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1054,30 +1054,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>朱森林</t>
+          <t>卢瑞华</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>中共广州市委组织部办公室</t>
+          <t>中共佛山市委</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>副主任、主任</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1087,20 +1087,16 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>同机构先后任副主任、主任，含主任时应按正处级</t>
+          <t>佛山属地级市，市委副书记通常为副厅级。</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1112,30 +1108,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>朱森林</t>
+          <t>卢瑞华</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>广州市军管会组织办公室</t>
+          <t>全国人大常委会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>综合组长</t>
+          <t>委员</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1145,73 +1141,77 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>95</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>全国人大常委会普通委员通常为正部级，非副国级</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>卢瑞华</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>全国人大华侨委员会</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>副主任委员</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>副国级</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>采纳LLM1</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>90</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>军管会内设“综合组长”缺明确定级，信息不足</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>gpt-5.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>朱森林</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>广州市革委会组织办公室</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>综合组长</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>广州市革委会属地厅级，其组织办公室内设综合组长通常为处级</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>99</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>全国人大专门委员会副主任委员通常为副部级</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -1220,30 +1220,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>朱森林</t>
+          <t>李长春</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>花县革委会</t>
+          <t>哈尔滨工业大学</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>副主任</t>
+          <t>留校待分配</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1258,11 +1258,11 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>花县为县级，革委会副主任通常对应副处级</t>
+          <t>留校待分配属毕业待派遣状态，非任职级别</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1274,30 +1274,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>朱森林</t>
+          <t>李长春</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中共花县县委</t>
+          <t>辽宁省沈阳市开关厂</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>常委</t>
+          <t>技术员</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1307,16 +1307,16 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>县委常委属县级党委副职序列，通常为副处级</t>
+          <t>企业技术员非学生，且无明确行政参照级别</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1326,162 +1326,162 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>朱森林</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>10</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>从化县革委会</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>副主任</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>李长春</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>辽宁省沈阳市电器工业公司</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>革委会副主任、党委常委</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>副处级</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>采纳LLM1</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>92</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>县革委会相当于县政府，副主任通常对应副处级</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>市属工业公司革委会副主任通常对应副处级</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>朱森林</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>中共从化县委</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>常委</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>李长春</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>辽宁省沈阳市电器控制设备工业公司</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>副经理、经理、党委副书记</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>副处级</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>采纳LLM1</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>95</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>县委常委通常属县级党委副职，对应副处级</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>市属工业公司经理通常对应县处级，副经理至少副处</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>朱森林</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>广州市革委会宣传办公室</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>副主任</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>李长春</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>辽宁省沈阳市机电工业局</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>副局长、党委副书记</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>副处级</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>广州市革委会属地厅级，其宣传办公室副主任通常为正处级</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>94</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>地级市局为正处级，副局长通常副处级</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -1490,30 +1490,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>朱森林</t>
+          <t>李长春</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中共广州市委宣传部办公室</t>
+          <t>中共沈阳市委</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>副秘书长</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1523,16 +1523,16 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>市委宣传部办公室主任通常为部机关内设处室正职</t>
+          <t>副省级市市委副秘书长通常为正处级，非市领导</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1544,25 +1544,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>朱森林</t>
+          <t>李长春</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中共广州市委</t>
+          <t>沈阳市经委</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>常委</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1577,16 +1577,16 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>广州市为副省级市，市委常委通常对应副厅级</t>
+          <t>沈阳市经委属地级市政府组成部门，主任通常正局级即正厅级</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1598,30 +1598,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>卢瑞华</t>
+          <t>李长春</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>广东省佛山市分析仪器厂</t>
+          <t>辽宁省政府</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>厂长</t>
+          <t>代省长</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1636,11 +1636,11 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>仅知厂长和厂名，单位隶属规模不明，难定级</t>
+          <t>省政府代省长视同省长，属正部级</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1652,30 +1652,30 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>卢瑞华</t>
+          <t>李长春</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中共佛山市委</t>
+          <t>河南省政府</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>代省长</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1685,16 +1685,16 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>佛山属地级市，市委副书记通常为副厅级。</t>
+          <t>省政府代省长视同省长，属正部级</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1706,30 +1706,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>卢瑞华</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>全国人大常委会</t>
+          <t>吉林省汪清县罗子沟公社太平大队</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>委员</t>
+          <t>知青</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1739,20 +1739,16 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>全国人大常委会普通委员通常为正部级，非副国级</t>
+          <t>知青属身份经历，非学生，无明确干部职级</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1764,30 +1760,30 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>卢瑞华</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>全国人大华侨委员会</t>
+          <t>延边大学朝鲜语系党总支</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>副主任委员</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1802,11 +1798,11 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>全国人大专门委员会副主任委员通常为副部级</t>
+          <t>高校系党总支副书记通常对应副处级</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1816,216 +1812,216 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>李长春</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>哈尔滨工业大学</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>留校待分配</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>张德江</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>中共延边大学委员会</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>常委</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>延边大学属地方本科高校，校党委常委通常为副厅级</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>张德江</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>延边大学革委会</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>副主任</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>大学革委会属校级领导层，副主任通常对应副厅级</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>张德江</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>留学生党支部</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>书记</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>难以判断</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>采纳LLM1</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>87</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>留校待分配属毕业待派遣状态，非任职级别</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>gpt-5.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>李长春</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>辽宁省沈阳市开关厂</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>技术员</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>90</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>企业技术员非学生，且无明确行政参照级别</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>gpt-5.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>李长春</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>辽宁省沈阳市电器工业公司</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>革委会副主任、党委常委</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>88</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>留学生党支部属学习期间学生党务，非行政级别</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>张德江</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>中共延吉市委</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>副处级</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>采纳LLM1</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>市属工业公司革委会副主任通常对应副处级</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>gpt-5.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>李长春</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>辽宁省沈阳市电器控制设备工业公司</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>副经理、经理、党委副书记</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>副处级</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>市属工业公司经理通常对应县处级，副经理至少副处</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>95</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>延吉为县级市，市委副书记通常副处级</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -2034,30 +2030,30 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>李长春</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>辽宁省沈阳市机电工业局</t>
+          <t>中共延边州委</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>副局长、党委副书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2072,11 +2068,11 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>地级市局为正处级，副局长通常副处级</t>
+          <t>延边州属地级行政区，州委副书记通常为副厅级</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2088,30 +2084,30 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>李长春</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>中共沈阳市委</t>
+          <t>中共延边州委</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>副秘书长</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2121,16 +2117,16 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>副省级市市委副秘书长通常为正处级，非市领导</t>
+          <t>延边州属副省级自治州，州委书记通常副部级</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2142,30 +2138,30 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>李长春</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>沈阳市经委</t>
+          <t>中共广东省委</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2180,11 +2176,11 @@
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>沈阳市经委属地级市政府组成部门，主任通常正局级即正厅级</t>
+          <t>省委书记属省部级正职，未给出兼任常委等副国级信息</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2196,25 +2192,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>李长春</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>辽宁省政府</t>
+          <t>中共重庆市委</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>代省长</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2234,11 +2230,11 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>省政府代省长视同省长，属正部级</t>
+          <t>直辖市委书记职务本身属正部级，未给出兼任政治局常委/委员信息</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2250,30 +2246,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>李长春</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>河南省政府</t>
+          <t>中共中央政治局</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>代省长</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2283,16 +2279,16 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>省政府代省长视同省长，属正部级</t>
+          <t>中共中央政治局常委属正国级。</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2308,26 +2304,26 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>吉林省汪清县罗子沟公社太平大队</t>
+          <t>国务院</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>知青</t>
+          <t>副总理、党组成员</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2342,11 +2338,11 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>知青属身份经历，非学生，无明确干部职级</t>
+          <t>国务院副总理属国家级副职，即副国级</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2362,26 +2358,26 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>延边大学朝鲜语系党总支</t>
+          <t>中共中央政治局</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2396,11 +2392,11 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>高校系党总支副书记通常对应副处级</t>
+          <t>中共中央政治局常委属正国级。</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2410,108 +2406,108 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>张德江</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>中共延边大学委员会</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>常委</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>延边大学属地方本科高校，校党委常委通常为副厅级</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>黄华华</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>13</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>国防大学</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>进修学员</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>86</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>国防大学进修属在职学习，通常保留原级别；黄华华当时已属副部级干部</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>张德江</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>延边大学革委会</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>副主任</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>大学革委会属校级领导层，副主任通常对应副厅级</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>黄华华</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>19</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>广州市人大常委会</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>主任</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>95</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>广州系副省级市，市人大常委会主任通常为副部级</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -2520,20 +2516,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>汪洋</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>留学生党支部</t>
+          <t>安徽省宿县地区食品厂</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>工人、车间负责人</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2553,16 +2549,16 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>留学生党支部属学习期间学生党务，非行政级别</t>
+          <t>企业工人、车间负责人非学生，“无”不当，级别不足以判断</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2572,54 +2568,54 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>张德江</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>11</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>中共延吉市委</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>副书记</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>副处级</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>汪洋</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>安徽省政府</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>省长助理</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>采纳LLM1</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
-        <v>95</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>延吉为县级市，市委副书记通常副处级</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>省长助理通常低于副省级，按厅局级高配看更接近正厅</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -2628,30 +2624,30 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>汪洋</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>中共延边州委</t>
+          <t>中共重庆市委</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2661,16 +2657,16 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>延边州属地级行政区，州委副书记通常为副厅级</t>
+          <t>重庆市委书记职务本身属正部级，未给出兼任政治局委员</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2682,30 +2678,30 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>汪洋</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>中共延边州委</t>
+          <t>重庆市人大常委会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2720,11 +2716,11 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>延边州属副省级自治州，州委书记通常副部级</t>
+          <t>直辖市人大常委会主任通常为正部级</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2736,30 +2732,30 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>汪洋</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>中共广东省委</t>
+          <t>中共中央政治局</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>正国级</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>副国级</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>正部级</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2774,11 +2770,11 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>省委书记属省部级正职，未给出兼任常委等副国级信息</t>
+          <t>中共中央政治局常委属副国级，非常设国家正职</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2790,30 +2786,30 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>汪洋</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>中共重庆市委</t>
+          <t>国务院</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副总理、党组成员</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>正国级</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>副国级</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>正部级</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2828,11 +2824,11 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>直辖市委书记职务本身属正部级，未给出兼任政治局常委/委员信息</t>
+          <t>国务院副总理属国家级副职，即副国级</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2844,11 +2840,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>汪洋</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2882,7 +2878,7 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2896,54 +2892,54 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>张德江</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>29</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>国务院</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>副总理、党组成员</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>正国级</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>副国级</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="n">
-        <v>99</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>国务院副总理属国家级副职，即副国级</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>朱小丹</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>共青团广州市委</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>干部、办公室副主任、主任</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>团市委属正处级单位，办公室主任通常正科至副处，含副主任、主任历程取最高可判正处</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -2952,30 +2948,30 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>朱小丹</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>中共中央政治局</t>
+          <t>共青团广州市委</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>常委</t>
+          <t>副书记、党组副书记</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2990,11 +2986,11 @@
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>中共中央政治局常委属正国级。</t>
+          <t>广州市为副省级市，团市委属副局级，副书记通常正处级</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3006,30 +3002,30 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>黄华华</t>
+          <t>朱小丹</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>国防大学</t>
+          <t>共青团广州市委</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>代书记、书记、党组书记</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3039,16 +3035,16 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>国防大学进修属在职学习，通常保留原级别；黄华华当时已属副部级干部</t>
+          <t>广州市为副省级市，团市委书记通常对应副局级即副厅级</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3060,30 +3056,30 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>黄华华</t>
+          <t>朱小丹</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>广州市人大常委会</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3093,16 +3089,20 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J49" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>广州系副省级市，市人大常委会主任通常为副部级</t>
+          <t>党校进修属在职保留级别，缺前后职务无法定</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3114,30 +3114,30 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>汪洋</t>
+          <t>朱小丹</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>安徽省宿县地区食品厂</t>
+          <t>中共广州市委</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>工人、车间负责人</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3147,16 +3147,16 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>企业工人、车间负责人非学生，“无”不当，级别不足以判断</t>
+          <t>广州市为副省级市，市委常委通常对应副厅级</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3166,54 +3166,54 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>汪洋</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>安徽省政府</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>省长助理</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>朱小丹</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>11</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>中共广州市委宣传部</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>部长</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>副部级</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>采纳LLM1</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>省长助理通常低于副省级，按厅局级高配看更接近正厅</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>98</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>广州市为副省级市，市委宣传部长通常为市委常委，正厅级</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -3222,30 +3222,30 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>汪洋</t>
+          <t>朱小丹</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>中共重庆市委</t>
+          <t>中共广州市委</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副书记、宣传部部长</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3255,16 +3255,16 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>重庆市委书记职务本身属正部级，未给出兼任政治局委员</t>
+          <t>广州市委副书记属副省级市市委副书记，通常正厅级</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3276,30 +3276,30 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>汪洋</t>
+          <t>朱小丹</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>重庆市人大常委会</t>
+          <t>中央党校研究生院</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>在职研究生</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3314,11 +3314,11 @@
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>直辖市人大常委会主任通常为正部级</t>
+          <t>在职研究生保留原级别，朱小丹该阶段已属副部级</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3330,30 +3330,30 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>汪洋</t>
+          <t>朱小丹</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>中共中央政治局</t>
+          <t>中共广州市委</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>常委</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3363,16 +3363,16 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>中共中央政治局常委属副国级，非常设国家正职</t>
+          <t>广州市为副省级市，市委副书记通常对应正厅级</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3384,30 +3384,30 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>汪洋</t>
+          <t>朱小丹</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>国务院</t>
+          <t>中共广东省委统战部</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>副总理、党组成员</t>
+          <t>常务副部长、部长</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3417,16 +3417,16 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>国务院副总理属国家级副职，即副国级</t>
+          <t>省委统战部为正厅级部门，常务副部长、部长属正厅级</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3438,30 +3438,30 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>汪洋</t>
+          <t>朱小丹</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>中共中央政治局</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>常委</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3471,16 +3471,16 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>中共中央政治局常委属正国级。</t>
+          <t>党校进修属在职学习，保留原级别；朱小丹时序已属省部级副职</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3490,54 +3490,54 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>朱小丹</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>共青团广州市委</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>干部、办公室副主任、主任</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>团市委属正处级单位，办公室主任通常正科至副处，含副主任、主任历程取最高可判正处</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="B57" t="n">
+        <v>32</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>中共广东省委</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="n">
+        <v>98</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>省委副书记属省级党委副职，通常为副部级</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -3550,26 +3550,26 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>共青团广州市委</t>
+          <t>中共广东省委</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>副书记、党组副书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3579,16 +3579,16 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>广州市为副省级市，团市委属副局级，副书记通常正处级</t>
+          <t>省委副书记属省级党委副职，通常为副部级</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3604,26 +3604,26 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>共青团广州市委</t>
+          <t>第十二届全国人大财政经济委员会</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>代书记、书记、党组书记</t>
+          <t>副主任委员</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3638,11 +3638,11 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>广州市为副省级市，团市委书记通常对应副局级即副厅级</t>
+          <t>全国人大专门委员会副主任委员通常为副部级</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3658,26 +3658,26 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>全国政协</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3687,20 +3687,16 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>党校进修属在职保留级别，缺前后职务无法定</t>
+          <t>全国政协常委属副国级机构常委，通常按正部级</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3716,26 +3712,26 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>中共广州市委</t>
+          <t>全国政协港澳台侨委员会</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>常委</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3750,11 +3746,11 @@
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>广州市为副省级市，市委常委通常对应副厅级</t>
+          <t>全国政协专门委员会主任通常为正部级，非副国级</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3770,26 +3766,26 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>中共广州市委宣传部</t>
+          <t>中央生态环境保护督察辽宁、吉林组</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>部长</t>
+          <t>组长</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3804,11 +3800,11 @@
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>广州市为副省级市，市委宣传部长通常为市委常委，正厅级</t>
+          <t>中央督察组组长通常由正部级干部担任，非副国级职务</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3820,25 +3816,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>朱小丹</t>
+          <t>胡春华</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>中共广州市委</t>
+          <t>中共西藏自治区山南地委</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>副书记、宣传部部长</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3858,11 +3854,11 @@
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>广州市委副书记属副省级市市委副书记，通常正厅级</t>
+          <t>山南地委属地级党委，副书记通常为副厅级</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3872,54 +3868,54 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>朱小丹</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>13</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>中央党校研究生院</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>在职研究生</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>胡春华</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>中央党校</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>进修学员</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>采纳LLM2</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="n">
-        <v>91</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>在职研究生保留原级别，朱小丹该阶段已属副部级</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>中央党校进修保留原级别，胡春华时任团中央书记处书记属正厅</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -3928,7 +3924,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>朱小丹</t>
+          <t>胡春华</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3936,17 +3932,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>中共广州市委</t>
+          <t>中央党校研究生院</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>在职研究生班学员</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3961,16 +3957,16 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>广州市为副省级市，市委副书记通常对应正厅级</t>
+          <t>在职研究生保留原级别，胡春华当时已属副部级</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3982,7 +3978,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>朱小丹</t>
+          <t>胡春华</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3990,17 +3986,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>中共广东省委统战部</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>常务副部长、部长</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4015,16 +4011,16 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>省委统战部为正厅级部门，常务副部长、部长属正厅级</t>
+          <t>党校进修属在职学习，保留原级别；胡春华此阶段已属副部级</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4036,30 +4032,30 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>朱小丹</t>
+          <t>马兴瑞</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>中国空间技术研究院（五院）</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>副院长、党委委员</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4074,11 +4070,11 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>党校进修属在职学习，保留原级别；朱小丹时序已属省部级副职</t>
+          <t>五院属航天科技集团重要科研院所，副院长通常正厅级</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4090,20 +4086,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>朱小丹</t>
+          <t>马兴瑞</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>中共广东省委</t>
+          <t>广东省政府</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>副省长、代省长、党组书记</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4128,11 +4124,11 @@
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>省委副书记属省级党委副职，通常为副部级</t>
+          <t>广东省副省长、代省长时属省级政府副职，副部级</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4144,11 +4140,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>朱小丹</t>
+          <t>马兴瑞</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -4198,30 +4194,30 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>朱小丹</t>
+          <t>马兴瑞</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>第十二届全国人大财政经济委员会</t>
+          <t>中共新疆维吾尔自治区委</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>副主任委员</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4231,16 +4227,16 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>全国人大专门委员会副主任委员通常为副部级</t>
+          <t>自治区党委书记通常为正部级，非当然副国级</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4252,25 +4248,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>朱小丹</t>
+          <t>马兴瑞</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>全国政协</t>
+          <t>新疆生产建设兵团</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>常委</t>
+          <t>第一政委</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4294,7 +4290,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>全国政协常委属副国级机构常委，通常按正部级</t>
+          <t>兵团第一政委通常由新疆党委书记兼任，职务本身按正部级</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4306,32 +4302,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>朱小丹</t>
+          <t>马兴瑞</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>全国政协港澳台侨委员会</t>
+          <t>中共新疆维吾尔自治区委</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>书记、常委、委员</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>副国级</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>正部级</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>副国级</t>
-        </is>
-      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -4339,16 +4335,16 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>全国政协专门委员会主任通常为正部级，非副国级</t>
+          <t>新疆党委书记职务本身属正部级，未示政治局委员</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4360,30 +4356,30 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>朱小丹</t>
+          <t>李希</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>中央生态环境保护督察辽宁、吉林组</t>
+          <t>甘肃省两当县云屏公社</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>组长</t>
+          <t>知青</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4393,16 +4389,16 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>中央督察组组长通常由正部级干部担任，非副国级职务</t>
+          <t>知青属身份经历，非学生，原文不足定行政级别</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4414,30 +4410,30 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>胡春华</t>
+          <t>李希</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>中共西藏自治区山南地委</t>
+          <t>中共甘肃省委知识分子工作办公室</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>副主任</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>副厅级</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>副部级</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4452,11 +4448,11 @@
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>山南地委属地级党委，副书记通常为副厅级</t>
+          <t>省委内设办公室副主任通常为副处，知工办多按处级配副职</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4466,54 +4462,54 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>胡春华</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="n">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>李希</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
         <v>11</v>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>中央党校</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>进修学员</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>中共甘肃省委组织部</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>党政干部处处长</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>正厅级</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>中央党校进修保留原级别，胡春华时任团中央书记处书记属正厅</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>98</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>省委组织部内设处处长，通常为正处级</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -4522,7 +4518,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>胡春华</t>
+          <t>李希</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -4530,22 +4526,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>中央党校研究生院</t>
+          <t>中共兰州市委组织部</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>在职研究生班学员</t>
+          <t>部长</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4555,16 +4551,16 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>在职研究生保留原级别，胡春华当时已属副部级</t>
+          <t>省会市委组织部长通常兼市委常委，属副厅级</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4576,7 +4572,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>胡春华</t>
+          <t>李希</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4584,22 +4580,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>中共兰州市委</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4609,16 +4605,16 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>党校进修属在职学习，保留原级别；胡春华此阶段已属副部级</t>
+          <t>地级市市委副书记通常为副厅级，非主官</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4630,20 +4626,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>马兴瑞</t>
+          <t>李希</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>中国空间技术研究院（五院）</t>
+          <t>中共兰州市委组织部</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>副院长、党委委员</t>
+          <t>部长</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4663,16 +4659,16 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>五院属航天科技集团重要科研院所，副院长通常正厅级</t>
+          <t>省会市委组织部长通常兼市委常委，属副厅级</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -4684,30 +4680,30 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>马兴瑞</t>
+          <t>李希</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>广东省政府</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>副省长、代省长、党组书记</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4722,11 +4718,11 @@
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>广东省副省长、代省长时属省级政府副职，副部级</t>
+          <t>党校进修属在职学习，保留原级别，李希当时已至少正厅</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4738,25 +4734,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>马兴瑞</t>
+          <t>李希</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>中共广东省委</t>
+          <t>清华大学经济管理学院</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4771,16 +4767,16 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>省委副书记属省级党委副职，通常为副部级</t>
+          <t>学生属全日制学习经历，无行政级别</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4792,30 +4788,30 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>马兴瑞</t>
+          <t>李希</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>中共新疆维吾尔自治区委</t>
+          <t>辽宁省政府</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>代省长</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4825,16 +4821,16 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>自治区党委书记通常为正部级，非当然副国级</t>
+          <t>省政府代省长视同省长，属正部级</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -4846,20 +4842,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>马兴瑞</t>
+          <t>李希</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团</t>
+          <t>中共辽宁省委</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>第一政委</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4884,11 +4880,11 @@
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>兵团第一政委通常由新疆党委书记兼任，职务本身按正部级</t>
+          <t>省委书记属省部级正职，未示兼任政治局委员</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -4900,20 +4896,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>马兴瑞</t>
+          <t>李希</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>中共新疆维吾尔自治区委</t>
+          <t>辽宁省人大常委会</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>书记、常委、委员</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4938,11 +4934,11 @@
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>新疆党委书记职务本身属正部级，未示政治局委员</t>
+          <t>省人大常委会主任属省级正职，通常正部级</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -4958,26 +4954,26 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>甘肃省两当县云屏公社</t>
+          <t>中共广东省委</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>知青</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4992,11 +4988,11 @@
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>知青属身份经历，非学生，原文不足定行政级别</t>
+          <t>省委书记属省部级正职，未见兼任政治局常委等副国级信息</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5012,26 +5008,26 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>中共甘肃省委知识分子工作办公室</t>
+          <t>中共广东省委</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>副主任</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5041,16 +5037,16 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>省委内设办公室副主任通常为副处，知工办多按处级配副职</t>
+          <t>广东省委书记属省部级正职，通常为正部级</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5062,30 +5058,30 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>李希</t>
+          <t>王伟中</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>中共甘肃省委组织部</t>
+          <t>美国能源部国家气候变化研究办公室</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>党政干部处处长</t>
+          <t>客座分析家</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5095,16 +5091,16 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>省委组织部内设处处长，通常为正处级</t>
+          <t>客座分析家属学术访问身份，非行政任职，按无级别</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5116,25 +5112,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>李希</t>
+          <t>王伟中</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>中共兰州市委组织部</t>
+          <t>清华大学公共管理学院</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>部长</t>
+          <t>博士研究生</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5154,11 +5150,11 @@
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>省会市委组织部长通常兼市委常委，属副厅级</t>
+          <t>博士研究生属学习经历，全日制无行政级别</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5170,25 +5166,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>李希</t>
+          <t>王伟中</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>中共兰州市委</t>
+          <t>中共山西省直机关工委</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5203,16 +5199,16 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>地级市市委副书记通常为副厅级，非主官</t>
+          <t>省直机关工委属省委派出工作机关，书记通常正厅级</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5224,25 +5220,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>李希</t>
+          <t>王伟中</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>中共兰州市委组织部</t>
+          <t>中共山西省直机关工委</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>部长</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5257,16 +5253,16 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>省会市委组织部长通常兼市委常委，属副厅级</t>
+          <t>省直机关工委通常为省委派出机构，书记一般正厅级</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5278,30 +5274,30 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>李希</t>
+          <t>王伟中</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>广东省政府</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>党组书记、副省长、代理省长</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5316,11 +5312,11 @@
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>党校进修属在职学习，保留原级别，李希当时已至少正厅</t>
+          <t>代理省长按省长视同正职，属省部级副职</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5332,25 +5328,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>李希</t>
+          <t>王伟中</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>清华大学经济管理学院</t>
+          <t>横琴粤澳深度合作区</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5365,16 +5361,16 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>学生属全日制学习经历，无行政级别</t>
+          <t>横琴合作区主任通常由广东省副省级领导兼任，岗级一般副部</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5386,20 +5382,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>李希</t>
+          <t>王伟中</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>辽宁省政府</t>
+          <t>内蒙古党校（行政学院）</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>代省长</t>
+          <t>校长（院长）</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5409,7 +5405,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5419,16 +5415,16 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>省政府代省长视同省长，属正部级</t>
+          <t>省级党校校长通常由省委常委兼任，对应副部；此处仅校长不足到正部</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5440,30 +5436,30 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>李希</t>
+          <t>王伟中</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>中共辽宁省委</t>
+          <t>内蒙古党校（行政学院）</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>校长（院长）</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5478,11 +5474,11 @@
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>省委书记属省部级正职，未示兼任政治局委员</t>
+          <t>省级党校常务副校长多为正厅，校长常由省委副书记兼任</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5494,30 +5490,30 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>李希</t>
+          <t>黄坤明</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>辽宁省人大常委会</t>
+          <t>陆军三二八六六部队八十四分队</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>战士、副班长</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5532,11 +5528,11 @@
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>省人大常委会主任属省级正职，通常正部级</t>
+          <t>军队任职非学习经历；仅知战士、副班长，难准确定级</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5548,30 +5544,30 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>李希</t>
+          <t>黄坤明</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>中共广东省委</t>
+          <t>福建省龙岩地区行署</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>专员助理、副秘书长</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5586,11 +5582,11 @@
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>省委书记属省部级正职，未见兼任政治局常委等副国级信息</t>
+          <t>地委行署属地厅级，专员助理通常按副厅级。</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5602,30 +5598,30 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>李希</t>
+          <t>黄坤明</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>中共广东省委</t>
+          <t>福建省龙岩地区行署</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>专员助理</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5640,11 +5636,11 @@
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>广东省委书记属省部级正职，通常为正部级</t>
+          <t>地区行署属地厅级，专员助理通常按副厅级配备</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5656,30 +5652,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>王伟中</t>
+          <t>黄坤明</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>美国能源部国家气候变化研究办公室</t>
+          <t>中共永定县委</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>客座分析家</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5694,11 +5690,11 @@
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>客座分析家属学术访问身份，非行政任职，按无级别</t>
+          <t>永定县属县级行政区，县委书记通常为正处级</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -5710,7 +5706,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>王伟中</t>
+          <t>黄坤明</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -5718,22 +5714,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>清华大学公共管理学院</t>
+          <t>中共永定县委</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>博士研究生</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5743,16 +5739,16 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>博士研究生属学习经历，全日制无行政级别</t>
+          <t>永定县为县级，县委书记通常对应正处级</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -5764,25 +5760,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>王伟中</t>
+          <t>黄坤明</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>中共山西省直机关工委</t>
+          <t>中共龙岩市委</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5797,16 +5793,16 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>省直机关工委属省委派出工作机关，书记通常正厅级</t>
+          <t>地级市市委副书记通常为副厅级，非书记市长。</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -5818,25 +5814,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>王伟中</t>
+          <t>黄坤明</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>中共山西省直机关工委</t>
+          <t>中共湖州市委</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5851,16 +5847,16 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>省直机关工委通常为省委派出机构，书记一般正厅级</t>
+          <t>湖州为地级市，市委副书记通常为副厅级</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -5872,30 +5868,30 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>王伟中</t>
+          <t>黄坤明</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>广东省政府</t>
+          <t>中共湖州市委</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>党组书记、副省长、代理省长</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5905,16 +5901,16 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>代理省长按省长视同正职，属省部级副职</t>
+          <t>地级市市委副书记通常为副厅级，非市长不升格</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5926,30 +5922,30 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>王伟中</t>
+          <t>黄坤明</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>横琴粤澳深度合作区</t>
+          <t>中共浙江省委宣传部</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>部长</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5959,16 +5955,16 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>横琴合作区主任通常由广东省副省级领导兼任，岗级一般副部</t>
+          <t>省委宣传部长通常兼省委常委，属副部级</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -5980,30 +5976,30 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>王伟中</t>
+          <t>黄坤明</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>内蒙古党校（行政学院）</t>
+          <t>清华大学公共管理学院</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>校长（院长）</t>
+          <t>博士研究生</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6013,16 +6009,16 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>省级党校校长通常由省委常委兼任，对应副部；此处仅校长不足到正部</t>
+          <t>博士研究生属学习经历，全日制通常无行政级别</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6034,20 +6030,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>王伟中</t>
+          <t>黄坤明</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>内蒙古党校（行政学院）</t>
+          <t>中共中央宣传部</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>校长（院长）</t>
+          <t>主持常务工作的副部长</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6057,7 +6053,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6072,11 +6068,11 @@
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>省级党校常务副校长多为正厅，校长常由省委副书记兼任</t>
+          <t>中宣部副部长属副部级，主持常务工作通常不改变行政级别</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6092,26 +6088,26 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>陆军三二八六六部队八十四分队</t>
+          <t>中央精神文明建设指导委员会办公室</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>战士、副班长</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6126,11 +6122,11 @@
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>军队任职非学习经历；仅知战士、副班长，难准确定级</t>
+          <t>中央文明办主任通常为副部长级，机构常按副部级把握</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6146,26 +6142,26 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>福建省龙岩地区行署</t>
+          <t>中共中央宣传部</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>专员助理、副秘书长</t>
+          <t>部长</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6180,11 +6176,11 @@
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>地委行署属地厅级，专员助理通常按副厅级。</t>
+          <t>中宣部属党中央机关，部长通常为正部级</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6200,26 +6196,26 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>福建省龙岩地区行署</t>
+          <t>中共广东省委</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>专员助理</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6234,11 +6230,11 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>地区行署属地厅级，专员助理通常按副厅级配备</t>
+          <t>省委书记属省部级正职，未见兼任政治局委员</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6250,30 +6246,30 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>黄坤明</t>
+          <t>孟凡利</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>中共永定县委</t>
+          <t>山东经济学院会计系</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>教师</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6288,11 +6284,11 @@
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>永定县属县级行政区，县委书记通常为正处级</t>
+          <t>高校任职属工作经历，教师并非学生“无”级别</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6304,32 +6300,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>黄坤明</t>
+          <t>孟凡利</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>中共永定县委</t>
+          <t>烟台市政府</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>党组书记</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t>副厅级</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -6337,7 +6333,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -6346,7 +6342,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>永定县为县级，县委书记通常对应正处级</t>
+          <t>地级市政府党组书记通常由市长担任，属正厅级</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6358,15 +6354,15 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>黄坤明</t>
+          <t>孟凡利</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>中共龙岩市委</t>
+          <t>中共烟台市委</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6376,14 +6372,14 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t>副厅级</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
       <c r="G110" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -6391,7 +6387,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -6400,7 +6396,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>地级市市委副书记通常为副厅级，非书记市长。</t>
+          <t>地级市市委副书记通常为副厅级，非市长不高配</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6412,15 +6408,15 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>黄坤明</t>
+          <t>孟凡利</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>中共湖州市委</t>
+          <t>中共烟台市委</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6430,12 +6426,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t>副厅级</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>正厅级</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6450,11 +6446,11 @@
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>湖州为地级市，市委副书记通常为副厅级</t>
+          <t>地级市市委副书记通常为正厅级，烟台属地级市</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6466,30 +6462,30 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>黄坤明</t>
+          <t>孟凡利</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>中共湖州市委</t>
+          <t>中共烟台市委党校</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>校长</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6499,16 +6495,16 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>地级市市委副书记通常为副厅级，非市长不升格</t>
+          <t>地级市委党校为正处级事业单位，校长通常正处级</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6520,30 +6516,30 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>黄坤明</t>
+          <t>孟凡利</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>中共浙江省委宣传部</t>
+          <t>中共烟台市委党校</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>部长</t>
+          <t>校长</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6553,16 +6549,16 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>省委宣传部长通常兼省委常委，属副部级</t>
+          <t>地级市委党校校长通常由市委常委兼任才副厅，单写校长多为正处</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6574,25 +6570,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>黄坤明</t>
+          <t>孟凡利</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>清华大学公共管理学院</t>
+          <t>中共青岛市委</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>博士研究生</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6607,16 +6603,16 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>博士研究生属学习经历，全日制通常无行政级别</t>
+          <t>青岛系副省级市，市委副书记通常为副部级</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6628,20 +6624,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>黄坤明</t>
+          <t>孟凡利</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>中共中央宣传部</t>
+          <t>广东省人民代表大会</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>主持常务工作的副部长</t>
+          <t>省长</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6651,7 +6647,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6661,16 +6657,20 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>副国级</t>
+        </is>
+      </c>
       <c r="J115" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>中宣部副部长属副部级，主持常务工作通常不改变行政级别</t>
+          <t>省人大属省级机关，主任通常副国级；‘省长’应为笔误</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6680,162 +6680,174 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>黄坤明</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>36</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>中央精神文明建设指导委员会办公室</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>主任</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="n">
-        <v>93</v>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>中央文明办主任通常为副部长级，机构常按副部级把握</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>朱森林</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>中共广州市委组织部办公室</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>副主任、主任</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>副处级</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>同条含副主任、主任，缺任职先后拆分，无法唯一对应级别</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>黄坤明</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>39</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>中共中央宣传部</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>部长</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>副国级</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="n">
-        <v>95</v>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>中宣部属党中央机关，部长通常为正部级</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>朱森林</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>广州市军管会组织办公室</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>综合组长</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>副处级</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>军管会办公室综合组长通常对应处级内设负责人，较可能副处</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>黄坤明</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>41</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>中共广东省委</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>书记</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>副国级</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="n">
-        <v>98</v>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>省委书记属省部级正职，未见兼任政治局委员</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>朱森林</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>广州市革委会组织办公室</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>综合组长</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>“综合组长”非标准职级称谓，革委会时期机构级别与组别层级不足以准确定级</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -6844,30 +6856,30 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>孟凡利</t>
+          <t>朱森林</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>山东经济学院会计系</t>
+          <t>花县革委会</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>教师</t>
+          <t>副主任</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -6877,16 +6889,16 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>高校任职属工作经历，教师并非学生“无”级别</t>
+          <t>花县属县级，革委会副主任通常对应县级政府副职，为副处级</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -6896,54 +6908,54 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>孟凡利</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>朱森林</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>烟台市政府</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>党组书记</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="n">
-        <v>95</v>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>地级市政府党组书记通常由市长担任，属正厅级</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>中共广州市委宣传部办公室</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>主任</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>副处级</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>市委宣传部为正处级部门，办公室主任通常为正科内设正职或高配；广州市副省级，市委工作部门办公室主任一般按正处级看</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
@@ -6952,7 +6964,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>孟凡利</t>
+          <t>朱森林</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -6960,17 +6972,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>中共烟台市委</t>
+          <t>中共广州市越秀区委</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6990,11 +7002,11 @@
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>地级市市委副书记通常为副厅级，非市长不高配</t>
+          <t>越秀区属广州辖区，广州为副省级市，区委书记通常为副厅级</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7006,25 +7018,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>孟凡利</t>
+          <t>朱森林</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>中共烟台市委</t>
+          <t>广州市越秀区革委会</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7044,11 +7056,11 @@
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>地级市市委副书记通常为正厅级，烟台属地级市</t>
+          <t>越秀区属广州市市辖区，区革委会主任通常对应区政府正职，为正处级</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7060,30 +7072,30 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>孟凡利</t>
+          <t>朱森林</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>中共烟台市委党校</t>
+          <t>广州市越秀区武装部</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>校长</t>
+          <t>第一政委</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7093,16 +7105,16 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>地级市委党校为正处级事业单位，校长通常正处级</t>
+          <t>区武装部属县处级单位，第一政委通常由区委书记兼任，按就高可判正处级</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7114,30 +7126,30 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>孟凡利</t>
+          <t>朱森林</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>中共烟台市委党校</t>
+          <t>中共广州市委办公厅</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>校长</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>正处级</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7152,11 +7164,11 @@
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>地级市委党校校长通常由市委常委兼任才副厅，单写校长多为正处</t>
+          <t>副省级市市委办公厅主任通常为正厅级</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7168,20 +7180,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>孟凡利</t>
+          <t>朱森林</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>中共青岛市委</t>
+          <t>中共广州市委党校</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>校长</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7191,7 +7203,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7201,77 +7213,19 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>青岛系副省级市，市委副书记通常为副部级</t>
+          <t>广州市委党校通常为副厅级单位，校长一般按正职为正厅级</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
-        <is>
-          <t>gpt-5.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>孟凡利</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>44</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>广东省人民代表大会</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>省长</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>副国级</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>95</v>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>省人大属省级机关，主任通常副国级；‘省长’应为笔误</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
